--- a/sample_data/C_legacy_pos/i-3-PRODUCT ACTIVITY.xlsx
+++ b/sample_data/C_legacy_pos/i-3-PRODUCT ACTIVITY.xlsx
@@ -574,10 +574,10 @@
         <v>36.44</v>
       </c>
       <c r="L7" t="n">
-        <v>44.46</v>
+        <v>33.52</v>
       </c>
       <c r="M7" t="n">
-        <v>889.2</v>
+        <v>670.4</v>
       </c>
     </row>
     <row r="8">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>415</v>
+        <v>300</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -611,22 +611,22 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>415</v>
+        <v>276</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>32.33</v>
+        <v>34.64</v>
       </c>
       <c r="L8" t="n">
-        <v>39.44</v>
+        <v>42.26</v>
       </c>
       <c r="M8" t="n">
-        <v>16367.6</v>
+        <v>11663.76</v>
       </c>
     </row>
     <row r="9">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>231</v>
+        <v>153</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -660,22 +660,22 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>41.71</v>
+        <v>39.72</v>
       </c>
       <c r="L9" t="n">
-        <v>50.05</v>
+        <v>47.66</v>
       </c>
       <c r="M9" t="n">
-        <v>7457.45</v>
+        <v>6863.04</v>
       </c>
     </row>
     <row r="10">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -709,22 +709,22 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>52.51</v>
+        <v>52.32</v>
       </c>
       <c r="L10" t="n">
-        <v>61.96</v>
+        <v>61.74</v>
       </c>
       <c r="M10" t="n">
-        <v>1425.08</v>
+        <v>1296.54</v>
       </c>
     </row>
     <row r="11">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>579</v>
+        <v>534</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -758,22 +758,22 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>452</v>
+        <v>395</v>
       </c>
       <c r="K11" t="n">
-        <v>27.14</v>
+        <v>26.8</v>
       </c>
       <c r="L11" t="n">
-        <v>33.92</v>
+        <v>33.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4307.84</v>
+        <v>4656.5</v>
       </c>
     </row>
     <row r="12">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -813,13 +813,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="K12" t="n">
-        <v>32.79</v>
+        <v>33.39</v>
       </c>
       <c r="L12" t="n">
-        <v>30.17</v>
+        <v>40.4</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>158</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -856,22 +856,22 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K13" t="n">
-        <v>123.21</v>
+        <v>117.57</v>
       </c>
       <c r="L13" t="n">
-        <v>141.69</v>
+        <v>135.21</v>
       </c>
       <c r="M13" t="n">
-        <v>21253.5</v>
+        <v>6084.45</v>
       </c>
     </row>
     <row r="14">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -905,22 +905,22 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>89.55</v>
+        <v>88.52</v>
       </c>
       <c r="L14" t="n">
-        <v>102.98</v>
+        <v>101.8</v>
       </c>
       <c r="M14" t="n">
-        <v>1029.8</v>
+        <v>407.2</v>
       </c>
     </row>
     <row r="15">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>290</v>
+        <v>46</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -954,22 +954,22 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>109.12</v>
+        <v>104.32</v>
       </c>
       <c r="L15" t="n">
-        <v>127.67</v>
+        <v>122.05</v>
       </c>
       <c r="M15" t="n">
-        <v>21831.57</v>
+        <v>5370.2</v>
       </c>
     </row>
     <row r="16">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1003,22 +1003,22 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="K16" t="n">
-        <v>22.84</v>
+        <v>24.86</v>
       </c>
       <c r="L16" t="n">
-        <v>28.55</v>
+        <v>31.07</v>
       </c>
       <c r="M16" t="n">
-        <v>2997.75</v>
+        <v>1553.5</v>
       </c>
     </row>
     <row r="17">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1052,22 +1052,22 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
-        <v>75.23</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>87.27</v>
+        <v>87.34</v>
       </c>
       <c r="M17" t="n">
-        <v>6807.06</v>
+        <v>4803.7</v>
       </c>
     </row>
     <row r="18">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1107,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>161.13</v>
+        <v>171.16</v>
       </c>
       <c r="L18" t="n">
-        <v>183.69</v>
+        <v>195.12</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>518</v>
+        <v>264</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1150,22 +1150,22 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>427</v>
+        <v>253</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>87.51000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="L19" t="n">
-        <v>101.51</v>
+        <v>106.53</v>
       </c>
       <c r="M19" t="n">
-        <v>43344.77</v>
+        <v>26952.09</v>
       </c>
     </row>
     <row r="20">
@@ -1208,10 +1208,10 @@
         <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>66.42</v>
+        <v>65.7</v>
       </c>
       <c r="L20" t="n">
-        <v>78.38</v>
+        <v>77.53</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1248,22 +1248,22 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>76.75</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>90.56</v>
+        <v>90.78</v>
       </c>
       <c r="M21" t="n">
-        <v>13221.76</v>
+        <v>17429.76</v>
       </c>
     </row>
     <row r="22">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1297,22 +1297,22 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>95.78</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>111.1</v>
+        <v>112.47</v>
       </c>
       <c r="M22" t="n">
-        <v>15554</v>
+        <v>12034.29</v>
       </c>
     </row>
     <row r="23">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>406</v>
+        <v>467</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1346,22 +1346,22 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="K23" t="n">
-        <v>176.12</v>
+        <v>187.29</v>
       </c>
       <c r="L23" t="n">
-        <v>199.02</v>
+        <v>211.64</v>
       </c>
       <c r="M23" t="n">
-        <v>74632.5</v>
+        <v>77248.60000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1395,22 +1395,22 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="K24" t="n">
-        <v>202.29</v>
+        <v>217.19</v>
       </c>
       <c r="L24" t="n">
-        <v>226.56</v>
+        <v>243.25</v>
       </c>
       <c r="M24" t="n">
-        <v>33304.32</v>
+        <v>29190</v>
       </c>
     </row>
     <row r="25">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1444,22 +1444,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="K25" t="n">
-        <v>9.09</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>11.82</v>
+        <v>11.21</v>
       </c>
       <c r="M25" t="n">
-        <v>248.22</v>
+        <v>302.67</v>
       </c>
     </row>
     <row r="26">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1493,22 +1493,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K26" t="n">
-        <v>235.77</v>
+        <v>241.56</v>
       </c>
       <c r="L26" t="n">
-        <v>261.7</v>
+        <v>268.13</v>
       </c>
       <c r="M26" t="n">
-        <v>50769.8</v>
+        <v>38610.72</v>
       </c>
     </row>
     <row r="27">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1542,22 +1542,22 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="K27" t="n">
-        <v>46.79</v>
+        <v>44.08</v>
       </c>
       <c r="L27" t="n">
-        <v>56.15</v>
+        <v>52.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3649.75</v>
+        <v>3650.1</v>
       </c>
     </row>
     <row r="28">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>392</v>
+        <v>201</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1591,22 +1591,22 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>286</v>
+        <v>201</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>56.58</v>
+        <v>59.59</v>
       </c>
       <c r="L28" t="n">
-        <v>67.33</v>
+        <v>70.91</v>
       </c>
       <c r="M28" t="n">
-        <v>19256.38</v>
+        <v>14252.91</v>
       </c>
     </row>
     <row r="29">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1649,13 +1649,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>69.84999999999999</v>
+        <v>72.56</v>
       </c>
       <c r="L29" t="n">
-        <v>82.42</v>
+        <v>85.62</v>
       </c>
       <c r="M29" t="n">
-        <v>15742.22</v>
+        <v>17038.38</v>
       </c>
     </row>
     <row r="30">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>66</v>
+        <v>280</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1689,22 +1689,22 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K30" t="n">
-        <v>385.01</v>
+        <v>397.77</v>
       </c>
       <c r="L30" t="n">
-        <v>423.51</v>
+        <v>437.55</v>
       </c>
       <c r="M30" t="n">
-        <v>20328.48</v>
+        <v>83572.05</v>
       </c>
     </row>
     <row r="31">
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>269</v>
+        <v>137</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K31" t="n">
-        <v>313.89</v>
+        <v>306.03</v>
       </c>
       <c r="L31" t="n">
-        <v>348.42</v>
+        <v>339.69</v>
       </c>
       <c r="M31" t="n">
-        <v>62367.18</v>
+        <v>40083.42</v>
       </c>
     </row>
     <row r="32">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1793,13 +1793,13 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="K32" t="n">
-        <v>513.1900000000001</v>
+        <v>513.4</v>
       </c>
       <c r="L32" t="n">
-        <v>554.25</v>
+        <v>554.47</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1836,22 +1836,22 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K33" t="n">
-        <v>161.07</v>
+        <v>159.46</v>
       </c>
       <c r="L33" t="n">
-        <v>177.18</v>
+        <v>175.41</v>
       </c>
       <c r="M33" t="n">
-        <v>17718</v>
+        <v>13506.57</v>
       </c>
     </row>
     <row r="34">
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1885,22 +1885,22 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K34" t="n">
-        <v>131.97</v>
+        <v>143.73</v>
       </c>
       <c r="L34" t="n">
-        <v>153.09</v>
+        <v>166.73</v>
       </c>
       <c r="M34" t="n">
-        <v>2296.35</v>
+        <v>500.19</v>
       </c>
     </row>
     <row r="35">
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1934,22 +1934,22 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="K35" t="n">
-        <v>111.4</v>
+        <v>108.36</v>
       </c>
       <c r="L35" t="n">
-        <v>130.34</v>
+        <v>126.78</v>
       </c>
       <c r="M35" t="n">
-        <v>1824.76</v>
+        <v>1267.8</v>
       </c>
     </row>
     <row r="36">
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1983,22 +1983,22 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>30.46</v>
+        <v>31.89</v>
       </c>
       <c r="L36" t="n">
-        <v>37.77</v>
+        <v>39.54</v>
       </c>
       <c r="M36" t="n">
-        <v>944.25</v>
+        <v>672.1799999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>671</v>
+        <v>115</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2032,22 +2032,22 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>482</v>
+        <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>37.12</v>
+        <v>37.63</v>
       </c>
       <c r="L37" t="n">
-        <v>45.29</v>
+        <v>45.91</v>
       </c>
       <c r="M37" t="n">
-        <v>8559.809999999999</v>
+        <v>4591</v>
       </c>
     </row>
     <row r="38">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2090,13 +2090,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>73.91</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>88.69</v>
+        <v>85.62</v>
       </c>
       <c r="M38" t="n">
-        <v>21817.74</v>
+        <v>13099.86</v>
       </c>
     </row>
     <row r="39">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>645</v>
+        <v>235</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2130,22 +2130,22 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>469</v>
+        <v>85</v>
       </c>
       <c r="K39" t="n">
-        <v>37.62</v>
+        <v>37.32</v>
       </c>
       <c r="L39" t="n">
-        <v>45.9</v>
+        <v>45.53</v>
       </c>
       <c r="M39" t="n">
-        <v>8078.4</v>
+        <v>6829.5</v>
       </c>
     </row>
     <row r="40">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>257</v>
+        <v>97</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2179,22 +2179,22 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
-        <v>41.81</v>
+        <v>43.56</v>
       </c>
       <c r="L40" t="n">
-        <v>50.59</v>
+        <v>52.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3389.53</v>
+        <v>4374.93</v>
       </c>
     </row>
     <row r="41">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2228,22 +2228,22 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>458</v>
+        <v>390</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K41" t="n">
-        <v>47.76</v>
+        <v>50.75</v>
       </c>
       <c r="L41" t="n">
-        <v>57.79</v>
+        <v>61.41</v>
       </c>
       <c r="M41" t="n">
-        <v>26467.82</v>
+        <v>23949.9</v>
       </c>
     </row>
     <row r="42">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>241</v>
+        <v>83</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2277,22 +2277,22 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="K42" t="n">
-        <v>59.86</v>
+        <v>57.66</v>
       </c>
       <c r="L42" t="n">
-        <v>71.83</v>
+        <v>69.19</v>
       </c>
       <c r="M42" t="n">
-        <v>10199.86</v>
+        <v>3528.69</v>
       </c>
     </row>
     <row r="43">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2326,22 +2326,22 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="K43" t="n">
-        <v>84.18000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="L43" t="n">
-        <v>99.33</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>1291.29</v>
+        <v>794.3200000000001</v>
       </c>
     </row>
     <row r="44">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2375,22 +2375,22 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K44" t="n">
-        <v>62.42</v>
+        <v>59.89</v>
       </c>
       <c r="L44" t="n">
-        <v>74.28</v>
+        <v>71.27</v>
       </c>
       <c r="M44" t="n">
-        <v>222.84</v>
+        <v>1425.4</v>
       </c>
     </row>
     <row r="45">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2424,22 +2424,22 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>45.03</v>
+        <v>48.6</v>
       </c>
       <c r="L45" t="n">
-        <v>54.04</v>
+        <v>58.32</v>
       </c>
       <c r="M45" t="n">
-        <v>4053</v>
+        <v>5832</v>
       </c>
     </row>
     <row r="46">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2473,22 +2473,22 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="K46" t="n">
-        <v>433.86</v>
+        <v>423.78</v>
       </c>
       <c r="L46" t="n">
-        <v>472.91</v>
+        <v>461.92</v>
       </c>
       <c r="M46" t="n">
-        <v>9458.200000000001</v>
+        <v>1847.68</v>
       </c>
     </row>
     <row r="47">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>558</v>
+        <v>165</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2522,22 +2522,22 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>541</v>
+        <v>165</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>156.81</v>
+        <v>150.95</v>
       </c>
       <c r="L47" t="n">
-        <v>178.76</v>
+        <v>172.08</v>
       </c>
       <c r="M47" t="n">
-        <v>96709.16</v>
+        <v>28393.2</v>
       </c>
     </row>
     <row r="48">
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2571,22 +2571,22 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="K48" t="n">
-        <v>28.2</v>
+        <v>29.1</v>
       </c>
       <c r="L48" t="n">
-        <v>35.25</v>
+        <v>36.38</v>
       </c>
       <c r="M48" t="n">
-        <v>493.5</v>
+        <v>691.22</v>
       </c>
     </row>
     <row r="49">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>236</v>
+        <v>110</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2620,22 +2620,22 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="K49" t="n">
-        <v>24.83</v>
+        <v>26.24</v>
       </c>
       <c r="L49" t="n">
-        <v>31.04</v>
+        <v>32.8</v>
       </c>
       <c r="M49" t="n">
-        <v>4500.8</v>
+        <v>2427.2</v>
       </c>
     </row>
     <row r="50">
@@ -2660,31 +2660,31 @@
         </is>
       </c>
       <c r="E50" t="n">
+        <v>158</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>89</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
         <v>69</v>
       </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>60</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>9</v>
-      </c>
       <c r="K50" t="n">
-        <v>35.88</v>
+        <v>33.57</v>
       </c>
       <c r="L50" t="n">
-        <v>44.13</v>
+        <v>41.29</v>
       </c>
       <c r="M50" t="n">
-        <v>2647.8</v>
+        <v>3674.81</v>
       </c>
     </row>
     <row r="51">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K51" t="n">
-        <v>39.61</v>
+        <v>40.64</v>
       </c>
       <c r="L51" t="n">
-        <v>49.91</v>
+        <v>51.21</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2767,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K52" t="n">
-        <v>232.34</v>
+        <v>228.66</v>
       </c>
       <c r="L52" t="n">
-        <v>274.16</v>
+        <v>269.82</v>
       </c>
       <c r="M52" t="n">
-        <v>15901.28</v>
+        <v>27521.64</v>
       </c>
     </row>
     <row r="53">
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2816,22 +2816,22 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K53" t="n">
-        <v>49.97</v>
+        <v>49.81</v>
       </c>
       <c r="L53" t="n">
-        <v>61.96</v>
+        <v>61.76</v>
       </c>
       <c r="M53" t="n">
-        <v>7992.84</v>
+        <v>4879.04</v>
       </c>
     </row>
     <row r="54">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>359</v>
+        <v>547</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2865,22 +2865,22 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>359</v>
+        <v>502</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K54" t="n">
-        <v>96.93000000000001</v>
+        <v>94.16</v>
       </c>
       <c r="L54" t="n">
-        <v>116.32</v>
+        <v>112.99</v>
       </c>
       <c r="M54" t="n">
-        <v>41758.88</v>
+        <v>56720.98</v>
       </c>
     </row>
     <row r="55">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2920,13 +2920,13 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="K55" t="n">
-        <v>45.15</v>
+        <v>44.06</v>
       </c>
       <c r="L55" t="n">
-        <v>55.53</v>
+        <v>54.19</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K56" t="n">
-        <v>133.7</v>
+        <v>140.36</v>
       </c>
       <c r="L56" t="n">
-        <v>159.1</v>
+        <v>167.03</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>583</v>
+        <v>203</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -3012,22 +3012,22 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>436</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>163.73</v>
+        <v>163.81</v>
       </c>
       <c r="L57" t="n">
-        <v>198.11</v>
+        <v>198.21</v>
       </c>
       <c r="M57" t="n">
-        <v>29122.17</v>
+        <v>38254.53</v>
       </c>
     </row>
     <row r="58">
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3067,13 +3067,13 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K58" t="n">
-        <v>70.86</v>
+        <v>69.81</v>
       </c>
       <c r="L58" t="n">
-        <v>86.45</v>
+        <v>85.17</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3116,13 +3116,13 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K59" t="n">
-        <v>60.31</v>
+        <v>60.78</v>
       </c>
       <c r="L59" t="n">
-        <v>72.98</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3159,22 +3159,22 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>21.53</v>
+        <v>22.05</v>
       </c>
       <c r="L60" t="n">
-        <v>27.34</v>
+        <v>28</v>
       </c>
       <c r="M60" t="n">
-        <v>4101</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="61">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -3208,22 +3208,22 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K61" t="n">
-        <v>31.43</v>
+        <v>31.66</v>
       </c>
       <c r="L61" t="n">
-        <v>38.97</v>
+        <v>39.26</v>
       </c>
       <c r="M61" t="n">
-        <v>155.88</v>
+        <v>628.16</v>
       </c>
     </row>
     <row r="62">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3257,22 +3257,22 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="K62" t="n">
-        <v>672.15</v>
+        <v>671.3099999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>793.14</v>
+        <v>792.15</v>
       </c>
       <c r="M62" t="n">
-        <v>40450.14</v>
+        <v>91889.39999999999</v>
       </c>
     </row>
     <row r="63">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3306,22 +3306,22 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="K63" t="n">
-        <v>974.13</v>
+        <v>981.33</v>
       </c>
       <c r="L63" t="n">
-        <v>1129.99</v>
+        <v>1138.34</v>
       </c>
       <c r="M63" t="n">
-        <v>5649.95</v>
+        <v>18213.44</v>
       </c>
     </row>
     <row r="64">
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>246</v>
+        <v>119</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="K64" t="n">
-        <v>544.4400000000001</v>
+        <v>523.72</v>
       </c>
       <c r="L64" t="n">
-        <v>636.99</v>
+        <v>612.75</v>
       </c>
       <c r="M64" t="n">
-        <v>103829.37</v>
+        <v>55147.5</v>
       </c>
     </row>
     <row r="65">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>41</v>
+        <v>213</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3404,22 +3404,22 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="K65" t="n">
-        <v>700.73</v>
+        <v>735.59</v>
       </c>
       <c r="L65" t="n">
-        <v>819.85</v>
+        <v>860.64</v>
       </c>
       <c r="M65" t="n">
-        <v>31154.3</v>
+        <v>113604.48</v>
       </c>
     </row>
     <row r="66">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -3453,22 +3453,22 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K66" t="n">
-        <v>99.03</v>
+        <v>90.94</v>
       </c>
       <c r="L66" t="n">
-        <v>118.84</v>
+        <v>109.13</v>
       </c>
       <c r="M66" t="n">
-        <v>2020.28</v>
+        <v>2073.47</v>
       </c>
     </row>
     <row r="67">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3508,13 +3508,13 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K67" t="n">
-        <v>119.61</v>
+        <v>115.55</v>
       </c>
       <c r="L67" t="n">
-        <v>142.34</v>
+        <v>137.5</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -3551,22 +3551,22 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="K68" t="n">
-        <v>396.89</v>
+        <v>410.2</v>
       </c>
       <c r="L68" t="n">
-        <v>424.67</v>
+        <v>397.89</v>
       </c>
       <c r="M68" t="n">
-        <v>64974.51</v>
+        <v>19496.61</v>
       </c>
     </row>
     <row r="69">
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3606,13 +3606,13 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K69" t="n">
-        <v>218.82</v>
+        <v>211.36</v>
       </c>
       <c r="L69" t="n">
-        <v>212.26</v>
+        <v>224.04</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3649,22 +3649,22 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="K70" t="n">
-        <v>252.02</v>
+        <v>266.98</v>
       </c>
       <c r="L70" t="n">
-        <v>267.14</v>
+        <v>283</v>
       </c>
       <c r="M70" t="n">
-        <v>4808.52</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="71">
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -3704,13 +3704,13 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K71" t="n">
-        <v>145.75</v>
+        <v>143.1</v>
       </c>
       <c r="L71" t="n">
-        <v>174.9</v>
+        <v>171.72</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>512</v>
+        <v>291</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -3747,22 +3747,22 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>512</v>
+        <v>264</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K72" t="n">
-        <v>49.85</v>
+        <v>53.68</v>
       </c>
       <c r="L72" t="n">
-        <v>61.32</v>
+        <v>66.03</v>
       </c>
       <c r="M72" t="n">
-        <v>31395.84</v>
+        <v>17431.92</v>
       </c>
     </row>
     <row r="73">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>116</v>
+        <v>671</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3796,22 +3796,22 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>67</v>
+        <v>178</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>49</v>
+        <v>493</v>
       </c>
       <c r="K73" t="n">
-        <v>24.05</v>
+        <v>22.3</v>
       </c>
       <c r="L73" t="n">
-        <v>30.3</v>
+        <v>28.1</v>
       </c>
       <c r="M73" t="n">
-        <v>2030.1</v>
+        <v>5001.8</v>
       </c>
     </row>
     <row r="74">
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3851,13 +3851,13 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="K74" t="n">
-        <v>25.89</v>
+        <v>28.16</v>
       </c>
       <c r="L74" t="n">
-        <v>32.36</v>
+        <v>35.2</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -3894,22 +3894,22 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="K75" t="n">
-        <v>21.62</v>
+        <v>22</v>
       </c>
       <c r="L75" t="n">
-        <v>27.24</v>
+        <v>27.72</v>
       </c>
       <c r="M75" t="n">
-        <v>217.92</v>
+        <v>277.2</v>
       </c>
     </row>
     <row r="76">
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3943,22 +3943,22 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K76" t="n">
-        <v>30.06</v>
+        <v>28.15</v>
       </c>
       <c r="L76" t="n">
-        <v>37.27</v>
+        <v>34.91</v>
       </c>
       <c r="M76" t="n">
-        <v>149.08</v>
+        <v>279.28</v>
       </c>
     </row>
     <row r="77">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>278</v>
+        <v>171</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3992,22 +3992,22 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="K77" t="n">
-        <v>182.44</v>
+        <v>178.96</v>
       </c>
       <c r="L77" t="n">
-        <v>207.98</v>
+        <v>204.01</v>
       </c>
       <c r="M77" t="n">
-        <v>36604.48</v>
+        <v>29785.46</v>
       </c>
     </row>
     <row r="78">
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -4041,22 +4041,22 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K78" t="n">
-        <v>343.73</v>
+        <v>376.35</v>
       </c>
       <c r="L78" t="n">
-        <v>395.29</v>
+        <v>432.8</v>
       </c>
       <c r="M78" t="n">
-        <v>3952.9</v>
+        <v>7790.4</v>
       </c>
     </row>
     <row r="79">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -4090,22 +4090,22 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="K79" t="n">
-        <v>218.77</v>
+        <v>237.3</v>
       </c>
       <c r="L79" t="n">
-        <v>253.77</v>
+        <v>275.27</v>
       </c>
       <c r="M79" t="n">
-        <v>29437.32</v>
+        <v>31105.51</v>
       </c>
     </row>
     <row r="80">
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -4145,13 +4145,13 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K80" t="n">
-        <v>319.95</v>
+        <v>321.45</v>
       </c>
       <c r="L80" t="n">
-        <v>358.34</v>
+        <v>360.02</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -4188,22 +4188,22 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="K81" t="n">
-        <v>64.06999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>76.88</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M81" t="n">
-        <v>1076.32</v>
+        <v>557.76</v>
       </c>
     </row>
     <row r="82">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -4237,22 +4237,22 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="K82" t="n">
-        <v>96.68000000000001</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>115.05</v>
+        <v>118.75</v>
       </c>
       <c r="M82" t="n">
-        <v>1955.85</v>
+        <v>2137.5</v>
       </c>
     </row>
     <row r="83">
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>712</v>
+        <v>342</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -4286,22 +4286,22 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>509</v>
+        <v>342</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>383.64</v>
+        <v>386.7</v>
       </c>
       <c r="L83" t="n">
-        <v>429.68</v>
+        <v>433.1</v>
       </c>
       <c r="M83" t="n">
-        <v>218707.12</v>
+        <v>148120.2</v>
       </c>
     </row>
     <row r="84">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -4341,13 +4341,13 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K84" t="n">
-        <v>1658.15</v>
+        <v>1678.24</v>
       </c>
       <c r="L84" t="n">
-        <v>1823.97</v>
+        <v>1846.06</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>474</v>
+        <v>401</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>474</v>
+        <v>401</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -4393,13 +4393,13 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>87.52</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>113.78</v>
+        <v>112.97</v>
       </c>
       <c r="M85" t="n">
-        <v>53931.72</v>
+        <v>45300.97</v>
       </c>
     </row>
     <row r="86">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K86" t="n">
-        <v>61.45</v>
+        <v>58.13</v>
       </c>
       <c r="L86" t="n">
-        <v>82.95999999999999</v>
+        <v>78.48</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
